--- a/artfynd/A 48181-2021 artfynd.xlsx
+++ b/artfynd/A 48181-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48181-2021 artfynd.xlsx
+++ b/artfynd/A 48181-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1375,648 +1375,6 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>112605602</v>
-      </c>
-      <c r="B8" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Lillskog, Hls</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>526112</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6845995</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Färila</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>112605601</v>
-      </c>
-      <c r="B9" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Lillskog, Hls</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>526083</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6846058</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Färila</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>112605603</v>
-      </c>
-      <c r="B10" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Lillskog, Hls</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>526123</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6845965</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Färila</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>112605606</v>
-      </c>
-      <c r="B11" t="n">
-        <v>77608</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Lillskog, Hls</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>526085</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6846015</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Färila</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>112605605</v>
-      </c>
-      <c r="B12" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Lillskog, Hls</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>526075</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6845996</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Färila</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>112605600</v>
-      </c>
-      <c r="B13" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Lillskog, Hls</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>526084</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6846043</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Ljusdal</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Färila</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48181-2021 artfynd.xlsx
+++ b/artfynd/A 48181-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109910929</v>
+        <v>112605602</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526075.40746074</v>
+        <v>526112</v>
       </c>
       <c r="R2" t="n">
-        <v>6845996.256433357</v>
+        <v>6845994</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109910925</v>
+        <v>112605603</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526083.5908178999</v>
+        <v>526122</v>
       </c>
       <c r="R3" t="n">
-        <v>6846043.217119097</v>
+        <v>6845965</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109910930</v>
+        <v>112605605</v>
       </c>
       <c r="B4" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526084.7518598476</v>
+        <v>526075</v>
       </c>
       <c r="R4" t="n">
-        <v>6846015.276366998</v>
+        <v>6845996</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +947,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1026,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109910928</v>
+        <v>112605606</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>526122.6158086042</v>
+        <v>526085</v>
       </c>
       <c r="R5" t="n">
-        <v>6845964.87531613</v>
+        <v>6846015</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1049,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1143,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109910926</v>
+        <v>112605600</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>526082.5269055194</v>
+        <v>526084</v>
       </c>
       <c r="R6" t="n">
-        <v>6846058.368033672</v>
+        <v>6846043</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,19 +1151,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1260,37 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109910927</v>
+        <v>112605601</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>526112.4261644215</v>
+        <v>526082</v>
       </c>
       <c r="R7" t="n">
-        <v>6845994.642731673</v>
+        <v>6846058</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,19 +1253,9 @@
           <t>2022-10-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 48181-2021 artfynd.xlsx
+++ b/artfynd/A 48181-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605602</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605603</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605605</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605606</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605600</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,8 +1314,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605601</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>